--- a/Configs/GameConfig/Datas/fg/#RangeTarget-靶子类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RangeTarget-靶子类型.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>enemy_scout</t>
+          <t>enemy_scout,enemy_echo_hunter</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>enemy_jammer</t>
+          <t>enemy_jammer,enemy_decoy_relay,enemy_listen_node</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>enemy_repairbot,enemy_core_boss</t>
+          <t>enemy_repairbot,enemy_core_boss,enemy_prism,enemy_listener,enemy_mind_core</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/Configs/GameConfig/Datas/fg/#RangeTarget-靶子类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RangeTarget-靶子类型.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>enemy_armorbot,enemy_strider</t>
+          <t>enemy_armorbot,enemy_strider,enemy_siege_heavy,enemy_aa_gun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>enemy_jammer,enemy_decoy_relay,enemy_listen_node</t>
+          <t>enemy_jammer,enemy_decoy_relay,enemy_listen_node,enemy_minelayer,enemy_loader</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>enemy_repairbot,enemy_core_boss,enemy_prism,enemy_listener,enemy_mind_core</t>
+          <t>enemy_repairbot,enemy_core_boss,enemy_prism,enemy_listener,enemy_mind_core,enemy_airburst</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/Configs/GameConfig/Datas/fg/#RangeTarget-靶子类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RangeTarget-靶子类型.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>enemy_armorbot,enemy_strider,enemy_siege_heavy,enemy_aa_gun</t>
+          <t>enemy_armorbot,enemy_strider,enemy_siege_heavy,enemy_aa_gun,enemy_settling_tank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -760,7 +760,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>enemy_scout,enemy_echo_hunter</t>
+          <t>enemy_scout,enemy_echo_hunter,enemy_oil_crawler,enemy_deact_drone</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>enemy_jammer,enemy_decoy_relay,enemy_listen_node,enemy_minelayer,enemy_loader</t>
+          <t>enemy_jammer,enemy_decoy_relay,enemy_listen_node,enemy_minelayer,enemy_loader,enemy_corrosion_swarm,enemy_sprayer</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>enemy_repairbot,enemy_core_boss,enemy_prism,enemy_listener,enemy_mind_core,enemy_airburst</t>
+          <t>enemy_repairbot,enemy_core_boss,enemy_prism,enemy_listener,enemy_mind_core,enemy_airburst,enemy_ln2_pump</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/Configs/GameConfig/Datas/fg/#RangeTarget-靶子类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RangeTarget-靶子类型.xlsx
@@ -864,7 +864,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>enemy_repairbot,enemy_core_boss,enemy_prism,enemy_listener,enemy_mind_core,enemy_airburst,enemy_ln2_pump</t>
+          <t>enemy_repairbot,enemy_core_boss,enemy_prism,enemy_listener,enemy_mind_core,enemy_airburst,enemy_ln2_pump,enemy_baptism_tower</t>
         </is>
       </c>
       <c r="G8" t="n">
